--- a/FLORES DE ESTRADA/Septiembre/EDESUR Septiembre.xlsx
+++ b/FLORES DE ESTRADA/Septiembre/EDESUR Septiembre.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B9B5E9-1048-4CFA-A21E-F77730266CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D33A40-D7C6-4A87-B2D3-869031737DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -233,7 +233,7 @@
     <t>7-B</t>
   </si>
   <si>
-    <t>EDESUR - VENCIMIENTO 15/09</t>
+    <t>EDESUR - VENCIMIENTO 15/10</t>
   </si>
 </sst>
 </file>
@@ -241,10 +241,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="167" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="166" formatCode="0.00;[Red]0.00"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -334,7 +334,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,18 +375,6 @@
       <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -548,7 +536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -558,13 +546,13 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -572,60 +560,56 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -641,11 +625,8 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,9 +931,9 @@
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="10" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" hidden="1" customWidth="1"/>
@@ -970,21 +951,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="57"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="53"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -1126,8 +1107,8 @@
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="66">
-        <v>1574074.95</v>
+      <c r="C8" s="50">
+        <v>1371121.11</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -1178,7 +1159,7 @@
       </c>
       <c r="L9" s="15">
         <f>C8-J34</f>
-        <v>1250515.1940000001</v>
+        <v>1029931.6518000003</v>
       </c>
       <c r="M9" s="14" t="s">
         <v>19</v>
@@ -1208,10 +1189,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F10" s="18">
-        <v>19096.7</v>
-      </c>
-      <c r="G10" s="62">
         <v>19350</v>
+      </c>
+      <c r="G10" s="58">
+        <v>19700.2</v>
       </c>
       <c r="H10" s="19">
         <v>0</v>
@@ -1222,31 +1203,31 @@
       </c>
       <c r="J10" s="20">
         <f>(G10-F10)*93.78</f>
-        <v>23754.473999999933</v>
+        <v>32841.756000000067</v>
       </c>
       <c r="K10" s="21">
         <f>G10-F10</f>
-        <v>253.29999999999927</v>
+        <v>350.20000000000073</v>
       </c>
       <c r="L10" s="19">
         <f>L9*E10/100</f>
-        <v>61275.24450600001</v>
+        <v>50466.650938200022</v>
       </c>
       <c r="M10" s="19">
         <f>J10+L10+3</f>
-        <v>85032.718505999947</v>
+        <v>83311.406938200089</v>
       </c>
       <c r="N10" s="22">
         <f>J10/C7*100</f>
-        <v>30.434944266495751</v>
+        <v>42.077842408712449</v>
       </c>
       <c r="O10" s="23">
         <f>J10/L9*100</f>
-        <v>1.8995750002858365</v>
+        <v>3.1887315961795024</v>
       </c>
       <c r="P10" s="20">
         <f>C7*O10/100</f>
-        <v>1482.6182877230954</v>
+        <v>2488.8050108181014</v>
       </c>
       <c r="Q10" s="24">
         <v>0.31</v>
@@ -1260,47 +1241,47 @@
       <c r="A11" s="18">
         <v>2</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="39">
         <v>2</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="39">
         <v>3.89</v>
       </c>
-      <c r="F11" s="46">
-        <v>17073.900000000001</v>
-      </c>
-      <c r="G11" s="63">
+      <c r="F11" s="39">
+        <v>17143.900000000001</v>
+      </c>
+      <c r="G11" s="58">
         <f>F11+70</f>
-        <v>17143.900000000001</v>
-      </c>
-      <c r="H11" s="47">
-        <v>0</v>
-      </c>
-      <c r="I11" s="48">
+        <v>17213.900000000001</v>
+      </c>
+      <c r="H11" s="40">
+        <v>0</v>
+      </c>
+      <c r="I11" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="48">
+      <c r="J11" s="41">
         <f>(G11-F11)*93.78</f>
         <v>6564.6</v>
       </c>
-      <c r="K11" s="49">
+      <c r="K11" s="42">
         <f t="shared" ref="K11:K25" si="2">G11-F11</f>
         <v>70</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="40">
         <f>L9*E11/100</f>
-        <v>48645.041046600003</v>
-      </c>
-      <c r="M11" s="47">
+        <v>40064.341255020016</v>
+      </c>
+      <c r="M11" s="40">
         <f t="shared" ref="M11:M24" si="3">J11+L11+1</f>
-        <v>55210.641046600002</v>
+        <v>46629.941255020014</v>
       </c>
       <c r="N11" s="22" t="e">
         <f t="shared" ref="N11:N33" si="4">J11/C9*100</f>
@@ -1308,11 +1289,11 @@
       </c>
       <c r="O11" s="23">
         <f>L11/L9*100</f>
-        <v>3.8899999999999997</v>
+        <v>3.8900000000000006</v>
       </c>
       <c r="P11" s="20">
         <f>C7*O11/100</f>
-        <v>3036.145</v>
+        <v>3036.1450000000004</v>
       </c>
       <c r="Q11" s="24">
         <v>0.19</v>
@@ -1340,11 +1321,11 @@
         <v>4</v>
       </c>
       <c r="F12" s="39">
-        <v>11501.3</v>
-      </c>
-      <c r="G12" s="62">
+        <v>11586.3</v>
+      </c>
+      <c r="G12" s="58">
         <f>F12+85</f>
-        <v>11586.3</v>
+        <v>11671.3</v>
       </c>
       <c r="H12" s="40">
         <v>0</v>
@@ -1363,11 +1344,11 @@
       </c>
       <c r="L12" s="40">
         <f>L9*E12/100</f>
-        <v>50020.607760000006</v>
+        <v>41197.266072000013</v>
       </c>
       <c r="M12" s="40">
         <f t="shared" si="3"/>
-        <v>57992.907760000009</v>
+        <v>49169.566072000016</v>
       </c>
       <c r="N12" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1375,11 +1356,11 @@
       </c>
       <c r="O12" s="23">
         <f>J12/L9*100</f>
-        <v>0.63744127526370542</v>
+        <v>0.77396397965521757</v>
       </c>
       <c r="P12" s="20">
         <f>C7*O12/100</f>
-        <v>497.5229153433221</v>
+        <v>604.07888612089732</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
@@ -1399,10 +1380,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F13" s="39">
-        <v>28598.880000000001</v>
-      </c>
-      <c r="G13" s="62">
         <v>29144.799999999999</v>
+      </c>
+      <c r="G13" s="58">
+        <v>29605.7</v>
       </c>
       <c r="H13" s="26">
         <v>0</v>
@@ -1413,19 +1394,19 @@
       </c>
       <c r="J13" s="41">
         <f t="shared" si="5"/>
-        <v>51196.37759999984</v>
+        <v>43223.202000000136</v>
       </c>
       <c r="K13" s="42">
         <f t="shared" si="2"/>
-        <v>545.91999999999825</v>
+        <v>460.90000000000146</v>
       </c>
       <c r="L13" s="40">
         <f>L9*E13/100</f>
-        <v>61275.24450600001</v>
+        <v>50466.650938200022</v>
       </c>
       <c r="M13" s="40">
         <f t="shared" si="3"/>
-        <v>112472.62210599985</v>
+        <v>93690.852938200158</v>
       </c>
       <c r="N13" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1433,11 +1414,11 @@
       </c>
       <c r="O13" s="23">
         <f>J13/L9*100</f>
-        <v>4.0940228351995405</v>
+        <v>4.1967058614481276</v>
       </c>
       <c r="P13" s="20">
         <f>C7*O13/100</f>
-        <v>3195.3848228732413</v>
+        <v>3275.5289248602635</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1457,10 +1438,10 @@
         <v>3.89</v>
       </c>
       <c r="F14" s="39">
-        <v>6426</v>
-      </c>
-      <c r="G14" s="62">
         <v>6798</v>
+      </c>
+      <c r="G14" s="58">
+        <v>7104.9</v>
       </c>
       <c r="H14" s="26">
         <v>0</v>
@@ -1471,19 +1452,19 @@
       </c>
       <c r="J14" s="41">
         <f t="shared" si="5"/>
-        <v>34886.160000000003</v>
+        <v>28781.081999999966</v>
       </c>
       <c r="K14" s="42">
         <f t="shared" si="2"/>
-        <v>372</v>
+        <v>306.89999999999964</v>
       </c>
       <c r="L14" s="40">
         <f>L9*E14/100</f>
-        <v>48645.041046600003</v>
+        <v>40064.341255020016</v>
       </c>
       <c r="M14" s="40">
         <f t="shared" si="3"/>
-        <v>83532.201046600007</v>
+        <v>68846.423255019981</v>
       </c>
       <c r="N14" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1491,17 +1472,17 @@
       </c>
       <c r="O14" s="23">
         <f>J14/L9*100</f>
-        <v>2.7897429929188049</v>
+        <v>2.7944652394845408</v>
       </c>
       <c r="P14" s="20">
         <f>C7*O14/100</f>
-        <v>2177.3944059731275</v>
+        <v>2181.0801194176838</v>
       </c>
       <c r="R14">
         <v>2540.8200000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:25" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" s="48" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>6</v>
       </c>
@@ -1518,11 +1499,11 @@
         <v>4</v>
       </c>
       <c r="F15" s="39">
-        <v>13626.7</v>
-      </c>
-      <c r="G15" s="62">
+        <v>13896.7</v>
+      </c>
+      <c r="G15" s="58">
         <f>F15+270</f>
-        <v>13896.7</v>
+        <v>14166.7</v>
       </c>
       <c r="H15" s="40">
         <v>0</v>
@@ -1541,25 +1522,25 @@
       </c>
       <c r="L15" s="40">
         <f>L9*E15/100</f>
-        <v>50020.607760000006</v>
+        <v>41197.266072000013</v>
       </c>
       <c r="M15" s="40">
         <f t="shared" si="3"/>
-        <v>75342.207760000005</v>
-      </c>
-      <c r="N15" s="50" t="e">
+        <v>66518.866072000004</v>
+      </c>
+      <c r="N15" s="46" t="e">
         <f t="shared" si="4"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O15" s="51">
+      <c r="O15" s="47">
         <f>J15/L9*100</f>
-        <v>2.0248134626023582</v>
+        <v>2.4584738177283376</v>
       </c>
       <c r="P15" s="41">
         <f>C7*O15/100</f>
-        <v>1580.3669075611406</v>
-      </c>
-      <c r="Y15" s="53"/>
+        <v>1918.8388147369676</v>
+      </c>
+      <c r="Y15" s="49"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
@@ -1578,10 +1559,10 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="F16" s="18">
-        <v>19037</v>
-      </c>
-      <c r="G16" s="62">
         <v>19390</v>
+      </c>
+      <c r="G16" s="58">
+        <v>19618.5</v>
       </c>
       <c r="H16" s="19">
         <v>0</v>
@@ -1592,19 +1573,19 @@
       </c>
       <c r="J16" s="20">
         <f t="shared" si="5"/>
-        <v>33104.340000000004</v>
+        <v>21428.73</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>353</v>
+        <v>228.5</v>
       </c>
       <c r="L16" s="19">
         <f>L9*E16/100</f>
-        <v>61275.24450600001</v>
+        <v>50466.650938200022</v>
       </c>
       <c r="M16" s="19">
         <f t="shared" si="3"/>
-        <v>94380.584506000014</v>
+        <v>71896.380938200018</v>
       </c>
       <c r="N16" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1612,11 +1593,11 @@
       </c>
       <c r="O16" s="23">
         <f>J16/L9*100</f>
-        <v>2.647256119624565</v>
+        <v>2.0805972864849078</v>
       </c>
       <c r="P16" s="20">
         <f>C7*O16/100</f>
-        <v>2066.1834013669727</v>
+        <v>1623.9061821014704</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -1636,10 +1617,10 @@
         <v>3.89</v>
       </c>
       <c r="F17" s="18">
-        <v>6219.7</v>
-      </c>
-      <c r="G17" s="62">
         <v>6352.68</v>
+      </c>
+      <c r="G17" s="58">
+        <v>6990.37</v>
       </c>
       <c r="H17" s="26">
         <v>0</v>
@@ -1650,19 +1631,19 @@
       </c>
       <c r="J17" s="20">
         <f t="shared" si="5"/>
-        <v>12470.864400000044</v>
+        <v>59802.568199999965</v>
       </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>132.98000000000047</v>
+        <v>637.6899999999996</v>
       </c>
       <c r="L17" s="19">
         <f>L9*E17/100</f>
-        <v>48645.041046600003</v>
+        <v>40064.341255020016</v>
       </c>
       <c r="M17" s="19">
         <f t="shared" si="3"/>
-        <v>61116.905446600045</v>
+        <v>99867.909455019981</v>
       </c>
       <c r="N17" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1670,11 +1651,11 @@
       </c>
       <c r="O17" s="23">
         <f>J17/L9*100</f>
-        <v>0.99725812687726878</v>
+        <v>5.8064598845451219</v>
       </c>
       <c r="P17" s="20">
         <f>C7*O17/100</f>
-        <v>778.35996802770819</v>
+        <v>4531.9419398874679</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
@@ -1694,10 +1675,10 @@
         <v>4</v>
       </c>
       <c r="F18" s="39">
-        <v>21089</v>
-      </c>
-      <c r="G18" s="62">
         <v>21581.4</v>
+      </c>
+      <c r="G18" s="58">
+        <v>21845.1</v>
       </c>
       <c r="H18" s="45">
         <v>0</v>
@@ -1708,19 +1689,19 @@
       </c>
       <c r="J18" s="41">
         <f t="shared" si="5"/>
-        <v>46177.272000000135</v>
+        <v>24729.785999999727</v>
       </c>
       <c r="K18" s="42">
         <f t="shared" si="2"/>
-        <v>492.40000000000146</v>
+        <v>263.69999999999709</v>
       </c>
       <c r="L18" s="40">
         <f>L9*E18/100</f>
-        <v>50020.607760000006</v>
+        <v>41197.266072000013</v>
       </c>
       <c r="M18" s="40">
         <f t="shared" si="3"/>
-        <v>96198.879760000142</v>
+        <v>65928.052071999744</v>
       </c>
       <c r="N18" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1728,11 +1709,11 @@
       </c>
       <c r="O18" s="23">
         <f>J18/L9*100</f>
-        <v>3.6926598110570521</v>
+        <v>2.4011094286479837</v>
       </c>
       <c r="P18" s="20">
         <f>C7*O18/100</f>
-        <v>2882.1209825300293</v>
+        <v>1874.0659090597514</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
@@ -1752,10 +1733,10 @@
         <v>12.66</v>
       </c>
       <c r="F19" s="39">
-        <v>23559</v>
-      </c>
-      <c r="G19" s="62">
         <v>23741.3</v>
+      </c>
+      <c r="G19" s="58">
+        <v>23882.6</v>
       </c>
       <c r="H19" s="40">
         <v>0</v>
@@ -1766,19 +1747,19 @@
       </c>
       <c r="J19" s="41">
         <f t="shared" si="5"/>
-        <v>17096.093999999932</v>
+        <v>13251.113999999932</v>
       </c>
       <c r="K19" s="42">
         <f t="shared" si="2"/>
-        <v>182.29999999999927</v>
+        <v>141.29999999999927</v>
       </c>
       <c r="L19" s="40">
         <f>L9*E19/100</f>
-        <v>158315.22356040002</v>
+        <v>130389.34711788004</v>
       </c>
       <c r="M19" s="40">
         <f>J19+L19+1</f>
-        <v>175412.31756039994</v>
+        <v>143641.46111787998</v>
       </c>
       <c r="N19" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1786,11 +1767,11 @@
       </c>
       <c r="O19" s="23">
         <f>J19/L9*100</f>
-        <v>1.3671240527126238</v>
+        <v>1.2866012979444903</v>
       </c>
       <c r="P19" s="20">
         <f>C7*O19/100</f>
-        <v>1067.0403231422029</v>
+        <v>1004.1923130456747</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
@@ -1810,11 +1791,11 @@
         <v>7.75</v>
       </c>
       <c r="F20" s="39">
-        <v>18145.099999999999</v>
-      </c>
-      <c r="G20" s="62">
+        <v>18345.099999999999</v>
+      </c>
+      <c r="G20" s="58">
         <f>F20+200</f>
-        <v>18345.099999999999</v>
+        <v>18545.099999999999</v>
       </c>
       <c r="H20" s="26">
         <v>0</v>
@@ -1833,11 +1814,11 @@
       </c>
       <c r="L20" s="40">
         <f>L9*E20/100</f>
-        <v>96914.92753500001</v>
+        <v>79819.703014500032</v>
       </c>
       <c r="M20" s="40">
         <f t="shared" si="3"/>
-        <v>115671.92753500001</v>
+        <v>98576.703014500032</v>
       </c>
       <c r="N20" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1845,57 +1826,57 @@
       </c>
       <c r="O20" s="23">
         <f>J20/L9*100</f>
-        <v>1.4998618241498949</v>
+        <v>1.8210917168358056</v>
       </c>
       <c r="P20" s="20">
         <f>C7*O20/100</f>
-        <v>1170.642153748993</v>
+        <v>1421.3620849903464</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>12</v>
       </c>
-      <c r="B21" s="46">
+      <c r="B21" s="39">
         <v>12</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="39">
         <v>7.51</v>
       </c>
-      <c r="F21" s="46">
-        <v>15144.8</v>
-      </c>
-      <c r="G21" s="63">
+      <c r="F21" s="39">
         <v>15188.8</v>
       </c>
-      <c r="H21" s="65">
-        <v>0</v>
-      </c>
-      <c r="I21" s="48">
+      <c r="G21" s="58">
+        <v>15233</v>
+      </c>
+      <c r="H21" s="26">
+        <v>0</v>
+      </c>
+      <c r="I21" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="48">
+      <c r="J21" s="41">
         <f t="shared" si="5"/>
-        <v>4126.32</v>
-      </c>
-      <c r="K21" s="49">
+        <v>4145.0760000000682</v>
+      </c>
+      <c r="K21" s="42">
         <f t="shared" si="2"/>
-        <v>44</v>
-      </c>
-      <c r="L21" s="47">
+        <v>44.200000000000728</v>
+      </c>
+      <c r="L21" s="40">
         <f>L9*E21/100</f>
-        <v>93913.691069400011</v>
-      </c>
-      <c r="M21" s="47">
+        <v>77347.867050180022</v>
+      </c>
+      <c r="M21" s="40">
         <f t="shared" si="3"/>
-        <v>98041.011069400003</v>
+        <v>81493.943050180096</v>
       </c>
       <c r="N21" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1903,62 +1884,62 @@
       </c>
       <c r="O21" s="23">
         <f>J21/L9*100</f>
-        <v>0.32996960131297687</v>
+        <v>0.40246126942071975</v>
       </c>
       <c r="P21" s="20">
         <f>C7*O21/100</f>
-        <v>257.54127382477844</v>
+        <v>314.12102078287177</v>
       </c>
       <c r="S21">
         <f>G21-F21</f>
-        <v>44</v>
+        <v>44.200000000000728</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>13</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="39">
         <v>13</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="39">
         <v>4.45</v>
       </c>
-      <c r="F22" s="46">
-        <v>11221.2</v>
-      </c>
-      <c r="G22" s="63">
+      <c r="F22" s="39">
+        <v>11414.2</v>
+      </c>
+      <c r="G22" s="58">
         <f>F22+193</f>
-        <v>11414.2</v>
-      </c>
-      <c r="H22" s="65">
-        <v>0</v>
-      </c>
-      <c r="I22" s="48">
+        <v>11607.2</v>
+      </c>
+      <c r="H22" s="26">
+        <v>0</v>
+      </c>
+      <c r="I22" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="48">
+      <c r="J22" s="41">
         <f t="shared" si="5"/>
         <v>18099.54</v>
       </c>
-      <c r="K22" s="49">
+      <c r="K22" s="42">
         <f t="shared" si="2"/>
         <v>193</v>
       </c>
-      <c r="L22" s="47">
+      <c r="L22" s="40">
         <f>L9*E22/100</f>
-        <v>55647.926133000015</v>
-      </c>
-      <c r="M22" s="47">
+        <v>45831.958505100018</v>
+      </c>
+      <c r="M22" s="40">
         <f t="shared" si="3"/>
-        <v>73748.466133000009</v>
+        <v>63932.498505100019</v>
       </c>
       <c r="N22" s="22" t="e">
         <f t="shared" si="4"/>
@@ -1966,11 +1947,11 @@
       </c>
       <c r="O22" s="23">
         <f>J22/L9*100</f>
-        <v>1.4473666603046487</v>
+        <v>1.7573535067465527</v>
       </c>
       <c r="P22" s="20">
         <f>C7*O22/100</f>
-        <v>1129.6696783677783</v>
+        <v>1371.6144120156844</v>
       </c>
       <c r="S22">
         <f>G22-F22</f>
@@ -1996,7 +1977,8 @@
       <c r="F23" s="39">
         <v>20525.400000000001</v>
       </c>
-      <c r="G23" s="62">
+      <c r="G23" s="58">
+        <f>F23</f>
         <v>20525.400000000001</v>
       </c>
       <c r="H23" s="40">
@@ -2016,11 +1998,11 @@
       </c>
       <c r="L23" s="40">
         <f>L9*E23/100</f>
-        <v>77156.787469800009</v>
+        <v>63546.782916060023</v>
       </c>
       <c r="M23" s="40">
         <f>J23+L23+1</f>
-        <v>77157.787469800009</v>
+        <v>63547.782916060023</v>
       </c>
       <c r="N23" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2052,10 +2034,10 @@
         <v>4.45</v>
       </c>
       <c r="F24" s="39">
-        <v>30772.400000000001</v>
-      </c>
-      <c r="G24" s="62">
         <v>30932.2</v>
+      </c>
+      <c r="G24" s="58">
+        <v>31147.8</v>
       </c>
       <c r="H24" s="40">
         <v>0</v>
@@ -2066,19 +2048,19 @@
       </c>
       <c r="J24" s="41">
         <f t="shared" si="5"/>
-        <v>14986.043999999933</v>
+        <v>20218.967999999863</v>
       </c>
       <c r="K24" s="42">
         <f t="shared" si="2"/>
-        <v>159.79999999999927</v>
+        <v>215.59999999999854</v>
       </c>
       <c r="L24" s="40">
         <f>L9*E24/100</f>
-        <v>55647.926133000015</v>
+        <v>45831.958505100018</v>
       </c>
       <c r="M24" s="40">
         <f t="shared" si="3"/>
-        <v>70634.970132999952</v>
+        <v>66051.92650509988</v>
       </c>
       <c r="N24" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2086,11 +2068,11 @@
       </c>
       <c r="O24" s="23">
         <f>J24/L9*100</f>
-        <v>1.1983895974957608</v>
+        <v>1.9631368707489854</v>
       </c>
       <c r="P24" s="20">
         <f>C7*O24/100</f>
-        <v>935.34308084544125</v>
+        <v>1532.2283276195831</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2110,10 +2092,10 @@
         <v>9.19</v>
       </c>
       <c r="F25" s="39">
-        <v>11649.8</v>
-      </c>
-      <c r="G25" s="62">
         <v>11746.3</v>
+      </c>
+      <c r="G25" s="58">
+        <v>11917.5</v>
       </c>
       <c r="H25" s="40">
         <v>0</v>
@@ -2124,19 +2106,19 @@
       </c>
       <c r="J25" s="41">
         <f t="shared" si="5"/>
-        <v>9049.77</v>
+        <v>16055.136000000068</v>
       </c>
       <c r="K25" s="42">
         <f t="shared" si="2"/>
-        <v>96.5</v>
+        <v>171.20000000000073</v>
       </c>
       <c r="L25" s="40">
         <f>L9*E25/100</f>
-        <v>114922.34632860002</v>
+        <v>94650.718800420029</v>
       </c>
       <c r="M25" s="40">
         <f>J25+L25+1</f>
-        <v>123973.11632860002</v>
+        <v>110706.8548004201</v>
       </c>
       <c r="N25" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2144,11 +2126,11 @@
       </c>
       <c r="O25" s="23">
         <f>J25/L9*100</f>
-        <v>0.72368333015232433</v>
+        <v>1.5588545096114563</v>
       </c>
       <c r="P25" s="20">
         <f>C7*O25/100</f>
-        <v>564.83483918388913</v>
+        <v>1216.6859447517415</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2187,11 +2169,11 @@
       <c r="K26" s="40"/>
       <c r="L26" s="40">
         <f>L9*E26/100</f>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="M26" s="40">
         <f t="shared" ref="M26:M33" si="6">J26+L26</f>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N26" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2242,11 +2224,11 @@
       <c r="K27" s="37"/>
       <c r="L27" s="37">
         <f>L26</f>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="M27" s="37">
         <f t="shared" si="6"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N27" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2297,11 +2279,11 @@
       <c r="K28" s="37"/>
       <c r="L28" s="37">
         <f>L27</f>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="M28" s="37">
         <f t="shared" si="6"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N28" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2352,11 +2334,11 @@
       <c r="K29" s="40"/>
       <c r="L29" s="40">
         <f>L28</f>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="M29" s="40">
         <f t="shared" si="6"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N29" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2407,11 +2389,11 @@
       <c r="K30" s="19"/>
       <c r="L30" s="19">
         <f t="shared" ref="L30:L33" si="7">L29</f>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="M30" s="19">
         <f t="shared" si="6"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N30" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2462,11 +2444,11 @@
       <c r="K31" s="19"/>
       <c r="L31" s="19">
         <f t="shared" si="7"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="M31" s="19">
         <f t="shared" si="6"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N31" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2517,11 +2499,11 @@
       <c r="K32" s="40"/>
       <c r="L32" s="40">
         <f t="shared" si="7"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="M32" s="40">
         <f t="shared" si="6"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N32" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2540,43 +2522,43 @@
       <c r="A33" s="39">
         <v>24</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="39">
         <v>24</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="54" t="s">
+      <c r="D33" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="39">
         <v>1.18</v>
       </c>
-      <c r="F33" s="36">
-        <v>0</v>
-      </c>
-      <c r="G33" s="36">
-        <v>0</v>
-      </c>
-      <c r="H33" s="37">
-        <v>0</v>
-      </c>
-      <c r="I33" s="38">
+      <c r="F33" s="39">
+        <v>0</v>
+      </c>
+      <c r="G33" s="39">
+        <v>0</v>
+      </c>
+      <c r="H33" s="40">
+        <v>0</v>
+      </c>
+      <c r="I33" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="38">
+      <c r="J33" s="41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37">
+      <c r="K33" s="40"/>
+      <c r="L33" s="40">
         <f t="shared" si="7"/>
-        <v>14756.079289200001</v>
-      </c>
-      <c r="M33" s="37">
+        <v>12153.193491240005</v>
+      </c>
+      <c r="M33" s="40">
         <f t="shared" si="6"/>
-        <v>14756.079289200001</v>
+        <v>12153.193491240005</v>
       </c>
       <c r="N33" s="22" t="e">
         <f t="shared" si="4"/>
@@ -2608,19 +2590,19 @@
       </c>
       <c r="J34" s="30">
         <f>SUM(J10:J33)</f>
-        <v>323559.75599999988</v>
+        <v>341189.45819999982</v>
       </c>
       <c r="K34" s="29">
         <f>SUM(K10:K33)</f>
-        <v>3450.199999999998</v>
+        <v>3638.1899999999978</v>
       </c>
       <c r="L34" s="29">
         <f>SUM(L10:L33)</f>
-        <v>1250390.1424806004</v>
+        <v>1029828.6586348205</v>
       </c>
       <c r="M34" s="29">
         <f>SUM(M10:M33)</f>
-        <v>1573967.8984806004</v>
+        <v>1371036.1168348205</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="2" t="e">
@@ -2632,19 +2614,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="59"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="55"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="9"/>
@@ -2662,86 +2644,86 @@
       <c r="H37" s="5"/>
       <c r="K37" s="34">
         <f>J34+L34</f>
-        <v>1573949.8984806002</v>
+        <v>1371018.1168348202</v>
       </c>
       <c r="L37" s="34"/>
       <c r="O37" s="2"/>
     </row>
     <row r="38" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
-      <c r="J38" s="61"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
       <c r="O38" s="2"/>
     </row>
     <row r="39" spans="1:16" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61"/>
-      <c r="J39" s="61"/>
-      <c r="K39" s="61"/>
-      <c r="L39" s="61"/>
-      <c r="M39" s="61"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
       <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-      <c r="L40" s="61"/>
-      <c r="M40" s="61"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
       <c r="O40" s="2"/>
     </row>
     <row r="41" spans="1:16" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
-      <c r="J41" s="61"/>
-      <c r="K41" s="61"/>
-      <c r="L41" s="61"/>
-      <c r="M41" s="61"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="57"/>
       <c r="O41" s="2"/>
     </row>
     <row r="42" spans="1:16" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-      <c r="J42" s="61"/>
-      <c r="K42" s="61"/>
-      <c r="L42" s="61"/>
-      <c r="M42" s="61"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="57"/>
       <c r="O42" s="2"/>
     </row>
     <row r="43" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6613,21 +6595,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="57"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="53"/>
       <c r="N1" s="1"/>
       <c r="O1" s="2"/>
       <c r="P1" s="3"/>
@@ -8219,19 +8201,19 @@
       <c r="A35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="59"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="55"/>
       <c r="N35" s="31"/>
       <c r="O35" s="2" t="e">
         <f t="shared" si="8"/>
